--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-25).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-25).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 9.444,00</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>66.6</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.405,97</t>
+  </si>
+  <si>
+    <t>99.1</t>
+  </si>
+  <si>
+    <t>66.3</t>
   </si>
   <si>
     <t>6.32</t>
   </si>
   <si>
-    <t>20.9</t>
+    <t>21.0</t>
   </si>
   <si>
     <t>7.7</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>32.1%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>32.3%</t>
   </si>
   <si>
     <t>17.9%</t>
@@ -4912,7 +4912,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4942,14 +4942,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>10360.030000000001</v>
+      </c>
+      <c r="N24" s="6">
+        <v>116</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>5.1401176991150441</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>20.652355434782606</v>
+      </c>
+      <c r="R24" s="8">
+        <v>8.5481880434782607</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.28260869565217389</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -10785,7 +10797,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -10815,10 +10827,16 @@
         <v>58</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6"/>
+      <c r="M63" s="5">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6">
+        <v>101</v>
+      </c>
       <c r="O63" s="6"/>
-      <c r="P63" s="7"/>
+      <c r="P63" s="7">
+        <v>0.19288058252427187</v>
+      </c>
       <c r="Q63" s="8"/>
       <c r="R63" s="8"/>
       <c r="S63" s="8"/>
@@ -14611,7 +14629,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14639,14 +14657,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>8514.7600000000002</v>
+      </c>
+      <c r="N89" s="6">
+        <v>77</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>12.15458375</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>32.428493548387095</v>
+      </c>
+      <c r="R89" s="8">
+        <v>9.4747322580645168</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -32107,7 +32137,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -32137,35 +32167,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>2460.1199999999999</v>
+      </c>
+      <c r="N207" s="6">
+        <v>27</v>
+      </c>
+      <c r="O207" s="6">
+        <v>18</v>
+      </c>
+      <c r="P207" s="7">
+        <v>7.8086407407407412</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>21.717594444444444</v>
+      </c>
+      <c r="R207" s="8">
+        <v>6.9675944444444449</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-25).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-25).xlsx
@@ -935,91 +935,94 @@
     <t>214</t>
   </si>
   <si>
-    <t>29</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 9.405,97</t>
+    <t>R$ 9.363,67</t>
   </si>
   <si>
-    <t>99.1</t>
+    <t>98.6</t>
   </si>
   <si>
-    <t>66.3</t>
+    <t>66.6</t>
   </si>
   <si>
-    <t>6.32</t>
+    <t>6.40</t>
   </si>
   <si>
-    <t>21.0</t>
+    <t>21.1</t>
   </si>
   <si>
-    <t>7.7</t>
+    <t>7.8</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>32.3%</t>
+    <t>31.7%</t>
   </si>
   <si>
-    <t>17.9%</t>
+    <t>17.6%</t>
   </si>
   <si>
     <t>1.2%</t>
   </si>
   <si>
-    <t>0.3%</t>
+    <t>0.2%</t>
   </si>
   <si>
-    <t>2.9%</t>
+    <t>3.0%</t>
   </si>
   <si>
     <t>0.8%</t>
   </si>
   <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>6.0%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
     <t>6.2%</t>
   </si>
   <si>
-    <t>2.7%</t>
+    <t>2581.0</t>
   </si>
   <si>
-    <t>6.3%</t>
+    <t>2209.0</t>
   </si>
   <si>
-    <t>2500.0</t>
-  </si>
-  <si>
-    <t>2133.0</t>
-  </si>
-  <si>
-    <t>141.0</t>
+    <t>147.0</t>
   </si>
   <si>
     <t>30.0</t>
   </si>
   <si>
-    <t>350.0</t>
+    <t>378.0</t>
   </si>
   <si>
     <t>98.0</t>
   </si>
   <si>
-    <t>33.0</t>
+    <t>34.0</t>
   </si>
   <si>
-    <t>745.0</t>
+    <t>756.0</t>
   </si>
   <si>
-    <t>320.0</t>
+    <t>324.0</t>
   </si>
   <si>
-    <t>749.0</t>
+    <t>777.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>64.0</t>
+    <t>67.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2206,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2236,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>17094.07</v>
+      </c>
+      <c r="N6" s="6">
+        <v>164</v>
+      </c>
+      <c r="O6" s="6">
+        <v>132</v>
+      </c>
+      <c r="P6" s="7">
+        <v>11.305555757575757</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>19.994949242424241</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.7263886363636363</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.007575757575757576</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.007575757575757576</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.015151515151515152</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -3275,7 +3336,9 @@
       <c r="N13" s="6">
         <v>146</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>101</v>
+      </c>
       <c r="P13" s="7">
         <v>7.593036301369863</v>
       </c>
@@ -3285,31 +3348,75 @@
       <c r="R13" s="8">
         <v>9.5576670000000004</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.15841584158415842</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.29702970297029702</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.029702970297029702</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.049504950495049507</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.019801980198019802</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.0099009900990099011</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.17821782178217821</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>32</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>30</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>18</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.029702970297029702</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>3</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -6748,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6778,35 +6885,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>9305.6399999999994</v>
+      </c>
+      <c r="N36" s="6">
+        <v>122</v>
+      </c>
+      <c r="O36" s="6">
+        <v>94</v>
+      </c>
+      <c r="P36" s="7">
+        <v>9.0290983606557376</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>24.291135106382978</v>
+      </c>
+      <c r="R36" s="8">
+        <v>7.7044329787234034</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.34042553191489361</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.14893617021276595</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.14893617021276595</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7051,7 +7216,7 @@
         <v>3.3805547619047625</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.71111111111111114</v>
@@ -7630,7 +7795,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7660,35 +7825,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>8556.0400000000009</v>
+      </c>
+      <c r="N42" s="6">
+        <v>95</v>
+      </c>
+      <c r="O42" s="6">
+        <v>64</v>
+      </c>
+      <c r="P42" s="7">
+        <v>7.2072691489361702</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>28.975000000000001</v>
+      </c>
+      <c r="R42" s="8">
+        <v>15.76953125</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.265625</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.203125</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.09375</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8979,7 +9202,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9009,35 +9232,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>909.29999999999995</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
+      <c r="O51" s="6">
+        <v>4</v>
+      </c>
+      <c r="P51" s="7">
+        <v>4.3037000000000001</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>27.358325000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>15.320824999999999</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -16554,7 +16835,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16584,35 +16865,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>6985.2299999999996</v>
+      </c>
+      <c r="N102" s="6">
+        <v>68</v>
+      </c>
+      <c r="O102" s="6">
+        <v>50</v>
+      </c>
+      <c r="P102" s="7">
+        <v>13.962076811594203</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>29.206334000000002</v>
+      </c>
+      <c r="R102" s="8">
+        <v>8.9788888888888891</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -23815,7 +24154,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -23845,35 +24184,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>6597.5900000000001</v>
+      </c>
+      <c r="N151" s="6">
+        <v>71</v>
+      </c>
+      <c r="O151" s="6">
+        <v>57</v>
+      </c>
+      <c r="P151" s="7">
+        <v>4.8927225352112682</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>14.274854385964913</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.5260228070175441</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.61403508771929827</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.070175438596491224</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24796,7 +25193,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -24826,35 +25223,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>8312.9099999999999</v>
+      </c>
+      <c r="N158" s="6">
+        <v>73</v>
+      </c>
+      <c r="O158" s="6">
+        <v>62</v>
+      </c>
+      <c r="P158" s="7">
+        <v>9.8145833333333332</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>23.772580645161291</v>
+      </c>
+      <c r="R158" s="8">
+        <v>6.7771499999999998</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.11290322580645161</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30451,7 +30906,9 @@
       <c r="N195" s="6">
         <v>98</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>75</v>
+      </c>
       <c r="P195" s="7">
         <v>5.7119791666666666</v>
       </c>
@@ -30461,31 +30918,75 @@
       <c r="R195" s="8">
         <v>10.086222666666666</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.29333333333333333</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0.013333333333333334</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
@@ -33252,52 +33753,52 @@
         <v>321</v>
       </c>
       <c t="s" r="Z216" s="11">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="AA216" s="11">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="AB216" s="11">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="AC216" s="11">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="AD216" s="11">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="AE216" s="11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="AF216" s="11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="AG216" s="11">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="AH216" s="11">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="AI216" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AJ216" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AK216" s="11">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="AL216" s="11">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="AM216" s="11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33314,10 +33815,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>
